--- a/data/external/Knee_Replacement_Missing_Values_ExtendedVersion.xlsx
+++ b/data/external/Knee_Replacement_Missing_Values_ExtendedVersion.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sgbsmit-my.sharepoint.com/personal/ginoh_sgb-smit_group/Documents/Documents/GitHub/EAISI-NHS/data/external/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="67" documentId="8_{932606EB-9CC2-4277-B33E-A7EDB74F399C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{74DF7467-E2AE-4356-8CB3-41777F65FA6F}"/>
+  <xr:revisionPtr revIDLastSave="114" documentId="8_{932606EB-9CC2-4277-B33E-A7EDB74F399C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ED33E816-4BFD-4EFD-87FA-3D14772588B2}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$N$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$P$62</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="186">
   <si>
     <t>ColumnName</t>
   </si>
@@ -784,12 +784,41 @@
   <si>
     <t>Direction</t>
   </si>
+  <si>
+    <t>Correction made to?</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Adjustment (to be) made</t>
+  </si>
+  <si>
+    <t>Create dummy variables</t>
+  </si>
+  <si>
+    <t>Missing values are adjusted to value 0 (which equals No)</t>
+  </si>
+  <si>
+    <t>9 &gt; NAN</t>
+  </si>
+  <si>
+    <t>Create dummy variables
+9 &gt; NAN</t>
+  </si>
+  <si>
+    <t>Adjusted 2 &gt; 0
+9 &gt; NAN</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -805,13 +834,25 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -872,10 +913,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -892,15 +934,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -910,6 +943,15 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -917,36 +959,30 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Good" xfId="1" builtinId="26"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFDAEEF3"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFDAEEF3"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFDAEEF3"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1246,7 +1282,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N52"/>
+  <dimension ref="A1:P62"/>
   <sheetFormatPr defaultColWidth="20.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="41.140625" bestFit="1" customWidth="1"/>
@@ -1255,10 +1291,11 @@
     <col min="9" max="9" width="48.85546875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="57.7109375" customWidth="1"/>
     <col min="11" max="11" width="34.5703125" customWidth="1"/>
-    <col min="12" max="14" width="20.140625" style="5"/>
+    <col min="12" max="15" width="20.140625" style="5"/>
+    <col min="16" max="16" width="52.140625" style="19" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1301,8 +1338,14 @@
       <c r="N1" s="13" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="2" spans="1:14" s="2" customFormat="1" ht="90" x14ac:dyDescent="0.25">
+      <c r="O1" s="13" t="s">
+        <v>177</v>
+      </c>
+      <c r="P1" s="13" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" s="2" customFormat="1" ht="90" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
         <v>33</v>
       </c>
@@ -1341,8 +1384,14 @@
       <c r="N2" s="8" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="3" spans="1:14" s="2" customFormat="1" ht="90" x14ac:dyDescent="0.25">
+      <c r="O2" s="15" t="s">
+        <v>179</v>
+      </c>
+      <c r="P2" s="16" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" s="2" customFormat="1" ht="90" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>36</v>
       </c>
@@ -1381,8 +1430,14 @@
       <c r="N3" s="8" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="4" spans="1:14" s="2" customFormat="1" ht="90" x14ac:dyDescent="0.25">
+      <c r="O3" s="15" t="s">
+        <v>179</v>
+      </c>
+      <c r="P3" s="16" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" s="2" customFormat="1" ht="90" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
         <v>37</v>
       </c>
@@ -1421,8 +1476,14 @@
       <c r="N4" s="8" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="5" spans="1:14" s="2" customFormat="1" ht="90" x14ac:dyDescent="0.25">
+      <c r="O4" s="15" t="s">
+        <v>179</v>
+      </c>
+      <c r="P4" s="16" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" s="2" customFormat="1" ht="90" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
         <v>30</v>
       </c>
@@ -1461,8 +1522,14 @@
       <c r="N5" s="8" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="6" spans="1:14" s="2" customFormat="1" ht="90" x14ac:dyDescent="0.25">
+      <c r="O5" s="15" t="s">
+        <v>179</v>
+      </c>
+      <c r="P5" s="16" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" s="2" customFormat="1" ht="90" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
         <v>27</v>
       </c>
@@ -1501,8 +1568,14 @@
       <c r="N6" s="8" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="7" spans="1:14" s="2" customFormat="1" ht="90" x14ac:dyDescent="0.25">
+      <c r="O6" s="15" t="s">
+        <v>179</v>
+      </c>
+      <c r="P6" s="16" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" s="2" customFormat="1" ht="90" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
         <v>47</v>
       </c>
@@ -1539,8 +1612,14 @@
         <v>48</v>
       </c>
       <c r="N7" s="8"/>
-    </row>
-    <row r="8" spans="1:14" s="2" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="O7" s="15" t="s">
+        <v>179</v>
+      </c>
+      <c r="P7" s="16" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" s="2" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
         <v>23</v>
       </c>
@@ -1579,8 +1658,14 @@
         <v>1</v>
       </c>
       <c r="N8" s="11"/>
-    </row>
-    <row r="9" spans="1:14" s="2" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="O8" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="P8" s="17" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" s="2" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
         <v>15</v>
       </c>
@@ -1619,8 +1704,14 @@
         <v>1</v>
       </c>
       <c r="N9" s="11"/>
-    </row>
-    <row r="10" spans="1:14" s="2" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="O9" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="P9" s="17" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" s="2" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
         <v>12</v>
       </c>
@@ -1659,8 +1750,14 @@
         <v>1</v>
       </c>
       <c r="N10" s="11"/>
-    </row>
-    <row r="11" spans="1:14" s="2" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="O10" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="P10" s="17" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" s="2" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
         <v>14</v>
       </c>
@@ -1699,8 +1796,14 @@
         <v>1</v>
       </c>
       <c r="N11" s="11"/>
-    </row>
-    <row r="12" spans="1:14" s="2" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="O11" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="P11" s="17" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" s="2" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
         <v>19</v>
       </c>
@@ -1739,8 +1842,14 @@
         <v>1</v>
       </c>
       <c r="N12" s="11"/>
-    </row>
-    <row r="13" spans="1:14" s="2" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="O12" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="P12" s="17" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" s="2" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
         <v>13</v>
       </c>
@@ -1779,8 +1888,14 @@
         <v>1</v>
       </c>
       <c r="N13" s="11"/>
-    </row>
-    <row r="14" spans="1:14" s="2" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="O13" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="P13" s="17" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" s="2" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
         <v>10</v>
       </c>
@@ -1819,8 +1934,14 @@
         <v>1</v>
       </c>
       <c r="N14" s="11"/>
-    </row>
-    <row r="15" spans="1:14" s="2" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="O14" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="P14" s="17" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" s="2" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
         <v>18</v>
       </c>
@@ -1859,8 +1980,14 @@
         <v>1</v>
       </c>
       <c r="N15" s="11"/>
-    </row>
-    <row r="16" spans="1:14" s="2" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="O15" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="P15" s="17" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" s="2" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="9" t="s">
         <v>16</v>
       </c>
@@ -1899,8 +2026,14 @@
         <v>1</v>
       </c>
       <c r="N16" s="11"/>
-    </row>
-    <row r="17" spans="1:14" s="2" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="O16" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="P16" s="17" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" s="2" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
         <v>20</v>
       </c>
@@ -1939,8 +2072,14 @@
         <v>1</v>
       </c>
       <c r="N17" s="11"/>
-    </row>
-    <row r="18" spans="1:14" s="2" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="O17" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="P17" s="17" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" s="2" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
         <v>17</v>
       </c>
@@ -1979,8 +2118,14 @@
         <v>1</v>
       </c>
       <c r="N18" s="11"/>
-    </row>
-    <row r="19" spans="1:14" s="2" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="O18" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="P18" s="17" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" s="2" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="9" t="s">
         <v>11</v>
       </c>
@@ -2019,8 +2164,14 @@
         <v>1</v>
       </c>
       <c r="N19" s="11"/>
-    </row>
-    <row r="20" spans="1:14" s="2" customFormat="1" ht="105" x14ac:dyDescent="0.25">
+      <c r="O19" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="P19" s="17" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" s="2" customFormat="1" ht="105" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>52</v>
       </c>
@@ -2050,8 +2201,14 @@
       <c r="L20" s="4"/>
       <c r="M20" s="4"/>
       <c r="N20" s="4"/>
-    </row>
-    <row r="21" spans="1:14" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="O20" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="P20" s="18" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>51</v>
       </c>
@@ -2083,8 +2240,14 @@
       <c r="L21" s="4"/>
       <c r="M21" s="4"/>
       <c r="N21" s="4"/>
-    </row>
-    <row r="22" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O21" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="P21" s="20" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>46</v>
       </c>
@@ -2106,8 +2269,10 @@
       <c r="L22" s="4"/>
       <c r="M22" s="4"/>
       <c r="N22" s="4"/>
-    </row>
-    <row r="23" spans="1:14" s="2" customFormat="1" ht="90" x14ac:dyDescent="0.25">
+      <c r="O22" s="4"/>
+      <c r="P22" s="18"/>
+    </row>
+    <row r="23" spans="1:16" s="2" customFormat="1" ht="90" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>31</v>
       </c>
@@ -2142,8 +2307,12 @@
       <c r="N23" s="4" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="24" spans="1:14" s="2" customFormat="1" ht="90" x14ac:dyDescent="0.25">
+      <c r="O23" s="4"/>
+      <c r="P23" s="18" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" s="2" customFormat="1" ht="90" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>32</v>
       </c>
@@ -2178,8 +2347,12 @@
       <c r="N24" s="4" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="25" spans="1:14" s="2" customFormat="1" ht="90" x14ac:dyDescent="0.25">
+      <c r="O24" s="4"/>
+      <c r="P24" s="18" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" s="2" customFormat="1" ht="90" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>38</v>
       </c>
@@ -2214,8 +2387,12 @@
       <c r="N25" s="4" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="26" spans="1:14" s="2" customFormat="1" ht="90" x14ac:dyDescent="0.25">
+      <c r="O25" s="4"/>
+      <c r="P25" s="18" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" s="2" customFormat="1" ht="90" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>34</v>
       </c>
@@ -2250,8 +2427,12 @@
       <c r="N26" s="4" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="27" spans="1:14" s="2" customFormat="1" ht="90" x14ac:dyDescent="0.25">
+      <c r="O26" s="4"/>
+      <c r="P26" s="18" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" s="2" customFormat="1" ht="90" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>39</v>
       </c>
@@ -2286,8 +2467,12 @@
       <c r="N27" s="4" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="28" spans="1:14" s="2" customFormat="1" ht="90" x14ac:dyDescent="0.25">
+      <c r="O27" s="4"/>
+      <c r="P27" s="18" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" s="2" customFormat="1" ht="90" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>26</v>
       </c>
@@ -2322,8 +2507,12 @@
       <c r="N28" s="4" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="29" spans="1:14" s="2" customFormat="1" ht="90" x14ac:dyDescent="0.25">
+      <c r="O28" s="4"/>
+      <c r="P28" s="18" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" s="2" customFormat="1" ht="90" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>35</v>
       </c>
@@ -2358,8 +2547,12 @@
       <c r="N29" s="4" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="30" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O29" s="4"/>
+      <c r="P29" s="18" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>24</v>
       </c>
@@ -2378,8 +2571,10 @@
       <c r="L30" s="4"/>
       <c r="M30" s="4"/>
       <c r="N30" s="4"/>
-    </row>
-    <row r="31" spans="1:14" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="O30" s="4"/>
+      <c r="P30" s="18"/>
+    </row>
+    <row r="31" spans="1:16" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>21</v>
       </c>
@@ -2407,8 +2602,10 @@
       <c r="L31" s="4"/>
       <c r="M31" s="4"/>
       <c r="N31" s="4"/>
-    </row>
-    <row r="32" spans="1:14" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="O31" s="4"/>
+      <c r="P31" s="18"/>
+    </row>
+    <row r="32" spans="1:16" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>44</v>
       </c>
@@ -2445,8 +2642,12 @@
       <c r="N32" s="4" t="s">
         <v>174</v>
       </c>
-    </row>
-    <row r="33" spans="1:14" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="O32" s="4"/>
+      <c r="P32" s="18" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>45</v>
       </c>
@@ -2483,8 +2684,12 @@
       <c r="N33" s="4" t="s">
         <v>174</v>
       </c>
-    </row>
-    <row r="34" spans="1:14" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="O33" s="4"/>
+      <c r="P33" s="18" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>40</v>
       </c>
@@ -2519,8 +2724,14 @@
         <v>1</v>
       </c>
       <c r="N34" s="4"/>
-    </row>
-    <row r="35" spans="1:14" s="2" customFormat="1" ht="105" x14ac:dyDescent="0.25">
+      <c r="O34" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="P34" s="20" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" s="2" customFormat="1" ht="105" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>9</v>
       </c>
@@ -2548,8 +2759,14 @@
       <c r="L35" s="4"/>
       <c r="M35" s="4"/>
       <c r="N35" s="4"/>
-    </row>
-    <row r="36" spans="1:14" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="O35" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="P35" s="20" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>49</v>
       </c>
@@ -2584,8 +2801,14 @@
         <v>1</v>
       </c>
       <c r="N36" s="4"/>
-    </row>
-    <row r="37" spans="1:14" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="O36" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="P36" s="20" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>48</v>
       </c>
@@ -2622,8 +2845,12 @@
       <c r="N37" s="4" t="s">
         <v>174</v>
       </c>
-    </row>
-    <row r="38" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O37" s="4"/>
+      <c r="P37" s="18" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>25</v>
       </c>
@@ -2642,8 +2869,10 @@
       <c r="L38" s="4"/>
       <c r="M38" s="4"/>
       <c r="N38" s="4"/>
-    </row>
-    <row r="39" spans="1:14" s="2" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="O38" s="4"/>
+      <c r="P38" s="18"/>
+    </row>
+    <row r="39" spans="1:16" s="2" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>50</v>
       </c>
@@ -2668,8 +2897,10 @@
       <c r="L39" s="4"/>
       <c r="M39" s="4"/>
       <c r="N39" s="4"/>
-    </row>
-    <row r="40" spans="1:14" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="O39" s="4"/>
+      <c r="P39" s="18"/>
+    </row>
+    <row r="40" spans="1:16" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>22</v>
       </c>
@@ -2694,8 +2925,10 @@
       <c r="L40" s="4"/>
       <c r="M40" s="4"/>
       <c r="N40" s="4"/>
-    </row>
-    <row r="41" spans="1:14" s="2" customFormat="1" ht="90" x14ac:dyDescent="0.25">
+      <c r="O40" s="4"/>
+      <c r="P40" s="18"/>
+    </row>
+    <row r="41" spans="1:16" s="2" customFormat="1" ht="90" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>41</v>
       </c>
@@ -2723,8 +2956,14 @@
       <c r="L41" s="4"/>
       <c r="M41" s="4"/>
       <c r="N41" s="4"/>
-    </row>
-    <row r="42" spans="1:14" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="O41" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="P41" s="20" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>42</v>
       </c>
@@ -2755,8 +2994,12 @@
       <c r="L42" s="4"/>
       <c r="M42" s="4"/>
       <c r="N42" s="4"/>
-    </row>
-    <row r="43" spans="1:14" s="2" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="O42" s="4"/>
+      <c r="P42" s="18" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" s="2" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>28</v>
       </c>
@@ -2781,8 +3024,10 @@
       <c r="L43" s="4"/>
       <c r="M43" s="4"/>
       <c r="N43" s="4"/>
-    </row>
-    <row r="44" spans="1:14" s="2" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+      <c r="O43" s="4"/>
+      <c r="P43" s="18"/>
+    </row>
+    <row r="44" spans="1:16" s="2" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>43</v>
       </c>
@@ -2813,8 +3058,12 @@
       <c r="L44" s="4"/>
       <c r="M44" s="4"/>
       <c r="N44" s="4"/>
-    </row>
-    <row r="45" spans="1:14" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="O44" s="4"/>
+      <c r="P44" s="18" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>29</v>
       </c>
@@ -2843,8 +3092,10 @@
       <c r="L45" s="4"/>
       <c r="M45" s="4"/>
       <c r="N45" s="4"/>
-    </row>
-    <row r="46" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O45" s="4"/>
+      <c r="P45" s="18"/>
+    </row>
+    <row r="46" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>6</v>
       </c>
@@ -2875,8 +3126,10 @@
       <c r="L46" s="4"/>
       <c r="M46" s="4"/>
       <c r="N46" s="4"/>
-    </row>
-    <row r="47" spans="1:14" s="2" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+      <c r="O46" s="4"/>
+      <c r="P46" s="18"/>
+    </row>
+    <row r="47" spans="1:16" s="2" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>5</v>
       </c>
@@ -2904,8 +3157,10 @@
       <c r="L47" s="4"/>
       <c r="M47" s="4"/>
       <c r="N47" s="4"/>
-    </row>
-    <row r="48" spans="1:14" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="O47" s="4"/>
+      <c r="P47" s="18"/>
+    </row>
+    <row r="48" spans="1:16" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>7</v>
       </c>
@@ -2939,8 +3194,10 @@
       <c r="L48" s="4"/>
       <c r="M48" s="4"/>
       <c r="N48" s="4"/>
-    </row>
-    <row r="49" spans="1:14" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="O48" s="4"/>
+      <c r="P48" s="18"/>
+    </row>
+    <row r="49" spans="1:16" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>8</v>
       </c>
@@ -2971,8 +3228,10 @@
       <c r="L49" s="4"/>
       <c r="M49" s="4"/>
       <c r="N49" s="4"/>
-    </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O49" s="4"/>
+      <c r="P49" s="18"/>
+    </row>
+    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>164</v>
       </c>
@@ -2989,7 +3248,7 @@
         <v>97.83</v>
       </c>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>165</v>
       </c>
@@ -3006,7 +3265,7 @@
         <v>88.53</v>
       </c>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>166</v>
       </c>
@@ -3023,8 +3282,14 @@
         <v>83.79</v>
       </c>
     </row>
+    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="F62">
+        <f>116407+21318</f>
+        <v>137725</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N52" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:P62" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
